--- a/src/python/ltr-cost-workbook/ltr-backup-storage-costs.xlsx
+++ b/src/python/ltr-cost-workbook/ltr-backup-storage-costs.xlsx
@@ -86,6 +86,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
@@ -97,11 +102,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -146,47 +146,48 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -700,7 +701,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10T06:32:45.497151+00:00  |  region: eastus  |  USD</t>
+          <t>2026-09-10T06:38:00.882590+00:00  |  region: eastus  |  USD</t>
         </is>
       </c>
     </row>
@@ -730,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1069,7 +1070,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>GRAND TOTAL</t>
+          <t>GRAND TOTAL (storage side)</t>
         </is>
       </c>
       <c r="B30" s="14">
@@ -1078,7 +1079,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Transfer plus retention.</t>
+          <t>Transfer plus retention. Does NOT include restore/export compute.</t>
         </is>
       </c>
     </row>
@@ -1121,10 +1122,23 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Banding check</t>
+        </is>
+      </c>
+      <c r="B37" s="17">
+        <f>IF(AND($B$8="Hot",$B$20&gt;51200),"Hot is volume-banded above 50 TB and this scenario exceeds it. The figures above use the first-band rate, so they are about 4% conservative.","OK - no volume banding applies at this tier and volume.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B37:C38"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1134,7 +1148,7 @@
       <formula1>"LRS,ZRS,GRS,GZRS,RA-GRS,RA-GZRS"</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=Prices!$A$29:$A$31</formula1>
+      <formula1>Prices!$A$29:$A$31</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1147,7 +1161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1157,6 +1171,8 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1169,655 +1185,799 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-10T06:32:45.497151+00:00 for region 'eastus' in USD. Product: General Block Blob v2. Data Stored is the first volume band (0-50 TB). Operation meters are not published for every redundancy; missing ones fall back to the LRS rate for the same tier.</t>
+          <t>Retrieved 2026-09-10T06:38:00.882590+00:00 for region 'eastus' in USD. Product: General Block Blob v2. Data Stored is the first volume band (0-50 TB). Only the Hot tier is volume-banded; Cool, Cold and Archive are flat. Operation meters are not published for every redundancy; missing ones are substituted from the closest published redundancy and flagged in the Substituted column.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Redundancy</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Stored $/GB/month</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Write $/10k ops</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Read $/10k ops</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Retrieval $/GB</t>
         </is>
       </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Volume banded?</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Substituted rates</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Hot GRS</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>GRS</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="20" t="n">
         <v>0.0458</v>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="21" t="n">
         <v>0.004</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="21" t="n">
         <v>0</v>
       </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>over 51,200 GB: $0.043968; over 512,000 GB: $0.042136</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Hot GZRS</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>GZRS</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>0.0468</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>0.1175</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="21" t="n">
         <v>0.004</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>0</v>
       </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>over 51,200 GB: $0.044928; over 512,000 GB: $0.043056</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Hot LRS</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>LRS</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>0.0208</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="21" t="n">
         <v>0.004</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="21" t="n">
         <v>0</v>
       </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>over 51,200 GB: $0.019968; over 512,000 GB: $0.019136</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Hot RA-GRS</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>RA-GRS</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>0.0589</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="21" t="n">
         <v>0.004</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="21" t="n">
         <v>0</v>
       </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>over 51,200 GB: $0.056544; over 512,000 GB: $0.054188</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Hot RA-GZRS</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>RA-GZRS</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="20" t="n">
         <v>0.0585</v>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F9" s="20" t="n">
+      <c r="E9" s="21" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="F9" s="21" t="n">
         <v>0.004</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <v>0</v>
       </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>over 51,200 GB: $0.056160; over 512,000 GB: $0.053820</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>write_usd_per_10k from GZRS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Hot ZRS</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>ZRS</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <v>0.026</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <v>0.0625</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="21" t="n">
         <v>0.004</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="21" t="n">
         <v>0</v>
       </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>over 51,200 GB: $0.024960; over 512,000 GB: $0.023920</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Cool GRS</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Cool</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>GRS</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>0.0334</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <v>0.01</v>
       </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Cool GZRS</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Cool</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>GZRS</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="20" t="n">
         <v>0.0342</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="21" t="n">
         <v>0.01</v>
       </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Cool LRS</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Cool</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>LRS</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="20" t="n">
         <v>0.0152</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="21" t="n">
         <v>0.01</v>
       </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Cool RA-GRS</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Cool</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>RA-GRS</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="20" t="n">
         <v>0.0425</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="21" t="n">
         <v>0.01</v>
       </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Cool RA-GZRS</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Cool</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>RA-GZRS</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="20" t="n">
         <v>0.04275</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>write_usd_per_10k from GZRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Cool ZRS</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Cool</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>ZRS</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="E16" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F16" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G16" s="21" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>Cool ZRS</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Cool</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Cold GRS</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>GRS</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Cold GZRS</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>GZRS</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Cold LRS</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>LRS</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Cold RA-GRS</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>RA-GRS</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Cold RA-GZRS</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>RA-GZRS</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Cold ZRS</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>ZRS</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="E16" s="20" t="n">
+      <c r="D22" s="20" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F22" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="F16" s="20" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G16" s="20" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Cold GRS</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="G22" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I22" s="19" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Archive GRS</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>GRS</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="E17" s="20" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F17" s="20" t="n">
+      <c r="D23" s="25" t="n">
+        <v>0.00299</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F23" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I23" s="19" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Archive LRS</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>LRS</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>0.00099</v>
+      </c>
+      <c r="E24" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="G17" s="20" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Cold GZRS</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>GZRS</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="E18" s="20" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>Cold LRS</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>LRS</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="E19" s="20" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F19" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G19" s="20" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>Cold RA-GRS</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="F24" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Archive RA-GRS</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>RA-GRS</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
-        <v>0.0101</v>
-      </c>
-      <c r="E20" s="20" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G20" s="20" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>Cold RA-GZRS</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>RA-GZRS</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>0.0106</v>
-      </c>
-      <c r="E21" s="20" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G21" s="20" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Cold ZRS</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>ZRS</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E22" s="20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G22" s="20" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Archive GRS</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>Archive</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>GRS</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="n">
+      <c r="D25" s="25" t="n">
         <v>0.00299</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E25" s="26" t="n">
         <v>0.21</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F25" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G25" s="26" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Archive LRS</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>Archive</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>LRS</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="n">
-        <v>0.00099</v>
-      </c>
-      <c r="E24" s="23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="23" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Archive RA-GRS</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>Archive</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>RA-GRS</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="n">
-        <v>0.00299</v>
-      </c>
-      <c r="E25" s="23" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F25" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="23" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="I25" s="19" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1827,44 +1987,44 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>$/GB</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Same region (any subscription)</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Cross region</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="21" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Out to the internet</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="21" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -1875,10 +2035,17 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Volume banding: the rest of this workbook prices everything at the first band. Only the Hot tier is banded, and the discount above 50 TB is roughly 4 percent, so for Hot scenarios above 50 TB the workbook is slightly conservative. Cool, Cold and Archive are flat at any volume.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1890,7 +2057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1920,940 +2087,940 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>1. TRANSFER COST (one time)  -  bandwidth plus write operations</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Backups \ Size (GB)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="29">
         <f>(10*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="29">
         <f>(10*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="29">
         <f>(10*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="29">
         <f>(10*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="29">
         <f>(10*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="29">
         <f>(10*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="29">
         <f>(10*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="29">
         <f>(10*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="29">
         <f>(25*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="29">
         <f>(25*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="29">
         <f>(25*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="29">
         <f>(25*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="29">
         <f>(25*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="29">
         <f>(25*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="29">
         <f>(25*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="29">
         <f>(25*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="29">
         <f>(50*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="29">
         <f>(50*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="29">
         <f>(50*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="29">
         <f>(50*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="29">
         <f>(50*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="29">
         <f>(50*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="29">
         <f>(50*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="29">
         <f>(50*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="29">
         <f>(100*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="29">
         <f>(100*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="29">
         <f>(100*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="29">
         <f>(100*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="29">
         <f>(100*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="29">
         <f>(100*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="29">
         <f>(100*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="29">
         <f>(100*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="28" t="n">
         <v>200</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="29">
         <f>(200*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="29">
         <f>(200*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="29">
         <f>(200*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="29">
         <f>(200*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="29">
         <f>(200*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="29">
         <f>(200*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="29">
         <f>(200*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="29">
         <f>(200*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="28" t="n">
         <v>400</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="29">
         <f>(400*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="29">
         <f>(400*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="29">
         <f>(400*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="29">
         <f>(400*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="29">
         <f>(400*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="29">
         <f>(400*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="29">
         <f>(400*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="29">
         <f>(400*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="28" t="n">
         <v>800</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="29">
         <f>(800*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="29">
         <f>(800*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="29">
         <f>(800*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="29">
         <f>(800*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="29">
         <f>(800*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="29">
         <f>(800*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="29">
         <f>(800*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="29">
         <f>(800*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>2. STORAGE COST over the full retention period</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Backups \ Size (GB)</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="29">
         <f>(10*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="29">
         <f>(10*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="29">
         <f>(10*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="29">
         <f>(10*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="29">
         <f>(10*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="29">
         <f>(10*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="29">
         <f>(10*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="29">
         <f>(10*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="29">
         <f>(25*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="29">
         <f>(25*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="29">
         <f>(25*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="29">
         <f>(25*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="29">
         <f>(25*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="29">
         <f>(25*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="29">
         <f>(25*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="29">
         <f>(25*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="29">
         <f>(50*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="29">
         <f>(50*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="29">
         <f>(50*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="29">
         <f>(50*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="29">
         <f>(50*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="29">
         <f>(50*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="29">
         <f>(50*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="29">
         <f>(50*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="29">
         <f>(100*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="29">
         <f>(100*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="29">
         <f>(100*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="29">
         <f>(100*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="29">
         <f>(100*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="29">
         <f>(100*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="29">
         <f>(100*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="29">
         <f>(100*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="n">
+      <c r="A21" s="28" t="n">
         <v>200</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="29">
         <f>(200*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="29">
         <f>(200*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="29">
         <f>(200*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="29">
         <f>(200*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="29">
         <f>(200*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="29">
         <f>(200*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="29">
         <f>(200*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="29">
         <f>(200*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="28" t="n">
         <v>400</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="29">
         <f>(400*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="29">
         <f>(400*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="29">
         <f>(400*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="29">
         <f>(400*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="29">
         <f>(400*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="29">
         <f>(400*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="29">
         <f>(400*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="29">
         <f>(400*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="n">
+      <c r="A23" s="28" t="n">
         <v>800</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="29">
         <f>(800*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="29">
         <f>(800*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="29">
         <f>(800*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="29">
         <f>(800*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="29">
         <f>(800*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="29">
         <f>(800*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="29">
         <f>(800*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="29">
         <f>(800*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>3. TOTAL  -  transfer plus storage</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Backups \ Size (GB)</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H27" s="18" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="n">
+      <c r="A28" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="29">
         <f>(10*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(10*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="29">
         <f>(10*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(10*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="29">
         <f>(10*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(10*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="29">
         <f>(10*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(10*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="29">
         <f>(10*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(10*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G28" s="26">
+      <c r="G28" s="29">
         <f>(10*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(10*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="29">
         <f>(10*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(10*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I28" s="26">
+      <c r="I28" s="29">
         <f>(10*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((10*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(10*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="n">
+      <c r="A29" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="29">
         <f>(25*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(25*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="29">
         <f>(25*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(25*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="29">
         <f>(25*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(25*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="29">
         <f>(25*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(25*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="29">
         <f>(25*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(25*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G29" s="26">
+      <c r="G29" s="29">
         <f>(25*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(25*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="29">
         <f>(25*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(25*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I29" s="26">
+      <c r="I29" s="29">
         <f>(25*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((25*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(25*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="n">
+      <c r="A30" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="29">
         <f>(50*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(50*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="29">
         <f>(50*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(50*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="29">
         <f>(50*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(50*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="29">
         <f>(50*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(50*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="29">
         <f>(50*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(50*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="29">
         <f>(50*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(50*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="29">
         <f>(50*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(50*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="29">
         <f>(50*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((50*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(50*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="n">
+      <c r="A31" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="29">
         <f>(100*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(100*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="29">
         <f>(100*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(100*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="29">
         <f>(100*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(100*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="29">
         <f>(100*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(100*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="29">
         <f>(100*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(100*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="29">
         <f>(100*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(100*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="29">
         <f>(100*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(100*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I31" s="26">
+      <c r="I31" s="29">
         <f>(100*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((100*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(100*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="n">
+      <c r="A32" s="28" t="n">
         <v>200</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="29">
         <f>(200*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(200*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="29">
         <f>(200*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(200*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="29">
         <f>(200*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(200*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="29">
         <f>(200*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(200*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="29">
         <f>(200*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(200*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G32" s="26">
+      <c r="G32" s="29">
         <f>(200*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(200*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="29">
         <f>(200*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(200*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I32" s="26">
+      <c r="I32" s="29">
         <f>(200*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((200*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(200*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="n">
+      <c r="A33" s="28" t="n">
         <v>400</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="29">
         <f>(400*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(400*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="29">
         <f>(400*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(400*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="29">
         <f>(400*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(400*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="29">
         <f>(400*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(400*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="29">
         <f>(400*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(400*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G33" s="26">
+      <c r="G33" s="29">
         <f>(400*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(400*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="29">
         <f>(400*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(400*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I33" s="26">
+      <c r="I33" s="29">
         <f>(400*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((400*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(400*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="n">
+      <c r="A34" s="28" t="n">
         <v>800</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="29">
         <f>(800*5/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*5/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(800*5/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="29">
         <f>(800*10/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*10/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(800*10/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="29">
         <f>(800*25/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*25/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(800*25/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="29">
         <f>(800*50/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*50/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(800*50/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="29">
         <f>(800*100/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*100/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(800*100/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="29">
         <f>(800*250/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*250/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(800*250/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="29">
         <f>(800*500/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*500/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(800*500/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="I34" s="26">
+      <c r="I34" s="29">
         <f>(800*1000/Parameters!$B$6)*Parameters!$B$16+ROUNDUP((800*1000/Parameters!$B$6)*1024/Parameters!$B$11,0)/10000*Parameters!$B$15+(800*1000/Parameters!$B$6)*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
@@ -2865,12 +3032,21 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Every cell uses the first-band storage rate. Only the Hot tier is volume-banded, so if the tier on 'Parameters' is Hot, cells whose artifact volume exceeds 50 TB (count x size / compression &gt; 51,200 GB) overstate the cost by roughly 4 percent. Cool, Cold and Archive are flat at any volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A38:I39"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A26:I26"/>
   </mergeCells>
@@ -2911,602 +3087,602 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Tier + redundancy</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Stored $/GB/mo</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Storage / month</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Storage over retention</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Transfer (one time)</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Read back once</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Hot GRS</t>
         </is>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Hot GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="29">
         <f>Parameters!$B$20*$B5</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="29">
         <f>$C5*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Hot GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="32">
         <f>$D5+$E5</f>
         <v/>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Hot GRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Hot GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Hot GZRS</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Hot GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="29">
         <f>Parameters!$B$20*$B6</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="29">
         <f>$C6*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Hot GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="32">
         <f>$D6+$E6</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Hot GZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Hot GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Hot LRS</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Hot LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="29">
         <f>Parameters!$B$20*$B7</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="29">
         <f>$C7*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Hot LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="32">
         <f>$D7+$E7</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Hot LRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Hot LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Hot RA-GRS</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Hot RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="29">
         <f>Parameters!$B$20*$B8</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="29">
         <f>$C8*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Hot RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="32">
         <f>$D8+$E8</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Hot RA-GRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Hot RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Hot RA-GZRS</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Hot RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="29">
         <f>Parameters!$B$20*$B9</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="29">
         <f>$C9*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Hot RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="32">
         <f>$D9+$E9</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Hot RA-GZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Hot RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Hot ZRS</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Hot ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="29">
         <f>Parameters!$B$20*$B10</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="29">
         <f>$C10*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Hot ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="32">
         <f>$D10+$E10</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Hot ZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Hot ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Cool GRS</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cool GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="29">
         <f>Parameters!$B$20*$B11</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="29">
         <f>$C11*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cool GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="32">
         <f>$D11+$E11</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cool GRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cool GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Cool GZRS</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cool GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="29">
         <f>Parameters!$B$20*$B12</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="29">
         <f>$C12*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cool GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="32">
         <f>$D12+$E12</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cool GZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cool GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Cool LRS</t>
         </is>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cool LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="29">
         <f>Parameters!$B$20*$B13</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="29">
         <f>$C13*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cool LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="32">
         <f>$D13+$E13</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cool LRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cool LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Cool RA-GRS</t>
         </is>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cool RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="29">
         <f>Parameters!$B$20*$B14</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="29">
         <f>$C14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cool RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="32">
         <f>$D14+$E14</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cool RA-GRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cool RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Cool RA-GZRS</t>
         </is>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cool RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="29">
         <f>Parameters!$B$20*$B15</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="29">
         <f>$C15*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cool RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="32">
         <f>$D15+$E15</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cool RA-GZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cool RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Cool ZRS</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cool ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="29">
         <f>Parameters!$B$20*$B16</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="29">
         <f>$C16*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cool ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="32">
         <f>$D16+$E16</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cool ZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cool ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Cold GRS</t>
         </is>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cold GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="29">
         <f>Parameters!$B$20*$B17</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="29">
         <f>$C17*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cold GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="32">
         <f>$D17+$E17</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cold GRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cold GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Cold GZRS</t>
         </is>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cold GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="29">
         <f>Parameters!$B$20*$B18</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="29">
         <f>$C18*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cold GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="32">
         <f>$D18+$E18</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cold GZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cold GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Cold LRS</t>
         </is>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cold LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="29">
         <f>Parameters!$B$20*$B19</f>
         <v/>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="29">
         <f>$C19*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cold LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="32">
         <f>$D19+$E19</f>
         <v/>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cold LRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cold LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Cold RA-GRS</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cold RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="29">
         <f>Parameters!$B$20*$B20</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="29">
         <f>$C20*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cold RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="32">
         <f>$D20+$E20</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cold RA-GRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cold RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Cold RA-GZRS</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cold RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="29">
         <f>Parameters!$B$20*$B21</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="29">
         <f>$C21*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cold RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="32">
         <f>$D21+$E21</f>
         <v/>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cold RA-GZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cold RA-GZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>Cold ZRS</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>INDEX(Prices!$D$5:$D$25,MATCH("Cold ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="29">
         <f>Parameters!$B$20*$B22</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="29">
         <f>$C22*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="29">
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Cold ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="32">
         <f>$D22+$E22</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="29">
         <f>Parameters!$B$20*INDEX(Prices!$G$5:$G$25,MATCH("Cold ZRS",Prices!$A$5:$A$25,0))+Parameters!$B$21/10000*INDEX(Prices!$F$5:$F$25,MATCH("Cold ZRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>Archive GRS</t>
         </is>
@@ -3527,7 +3703,7 @@
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Archive GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="34">
         <f>$D23+$E23</f>
         <v/>
       </c>
@@ -3537,7 +3713,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>Archive LRS</t>
         </is>
@@ -3558,7 +3734,7 @@
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Archive LRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="34">
         <f>$D24+$E24</f>
         <v/>
       </c>
@@ -3568,7 +3744,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>Archive RA-GRS</t>
         </is>
@@ -3589,7 +3765,7 @@
         <f>Parameters!$B$20*Parameters!$B$16+Parameters!$B$21/10000*INDEX(Prices!$E$5:$E$25,MATCH("Archive RA-GRS",Prices!$A$5:$A$25,0))</f>
         <v/>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="34">
         <f>$D25+$E25</f>
         <v/>
       </c>
@@ -3599,7 +3775,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Archive rows are highlighted: they are almost always the right answer for compliance copies that must exist but will probably never be read. Two caveats. Rehydration takes up to 15 hours at standard priority, and there is a 180-day minimum retention charge, so deleting early still bills you for 180 days.</t>
         </is>
@@ -3648,59 +3824,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Compression</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Artifact GB</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Storage over retention</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>What this looks like in practice</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="n">
+      <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="36">
         <f>Parameters!$B$19/$A5</f>
         <v/>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="29">
         <f>$B5*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="29">
         <f>$C5+$B5*Parameters!$B$16+ROUNDUP($B5*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>No compression at all.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="37" t="n">
         <v>1.02</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="38">
         <f>Parameters!$B$19/$A6</f>
         <v/>
       </c>
@@ -3712,161 +3888,161 @@
         <f>$C6+$B6*Parameters!$B$16+ROUNDUP($B6*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Measured worst case: already-compressed or encrypted data.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="35" t="n">
         <v>1.5</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="36">
         <f>Parameters!$B$19/$A7</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="29">
         <f>$B7*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="29">
         <f>$C7+$B7*Parameters!$B$16+ROUNDUP($B7*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Pessimistic.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="n">
+      <c r="A8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="36">
         <f>Parameters!$B$19/$A8</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="29">
         <f>$B8*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="29">
         <f>$C8+$B8*Parameters!$B$16+ROUNDUP($B8*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Conservative planning number.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n">
+      <c r="A9" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="36">
         <f>Parameters!$B$19/$A9</f>
         <v/>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="29">
         <f>$B9*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="29">
         <f>$C9+$B9*Parameters!$B$16+ROUNDUP($B9*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Typical native .bak with COMPRESSION.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="40">
         <f>Parameters!$B$19/$A10</f>
         <v/>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="41">
         <f>$B10*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="41">
         <f>$C10+$B10*Parameters!$B$16+ROUNDUP($B10*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>Default assumption in the toolkit. Unverified.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="36">
         <f>Parameters!$B$19/$A11</f>
         <v/>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="29">
         <f>$B11*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="29">
         <f>$C11+$B11*Parameters!$B$16+ROUNDUP($B11*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Optimistic; text-heavy schemas.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n">
+      <c r="A12" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="36">
         <f>Parameters!$B$19/$A12</f>
         <v/>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="29">
         <f>$B12*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="29">
         <f>$C12+$B12*Parameters!$B$16+ROUNDUP($B12*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Very repetitive data.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n">
+      <c r="A13" s="35" t="n">
         <v>33</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="36">
         <f>Parameters!$B$19/$A13</f>
         <v/>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="29">
         <f>$B13*Parameters!$B$14*Parameters!$B$7</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="29">
         <f>$C13+$B13*Parameters!$B$16+ROUNDUP($B13*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
         <v/>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Measured best case: highly repetitive test data. Do not plan on this.</t>
         </is>
@@ -3878,7 +4054,7 @@
           <t>Worst case vs default assumption:</t>
         </is>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="42">
         <f>IFERROR($D6/$D10,0)</f>
         <v/>
       </c>

--- a/src/python/ltr-cost-workbook/ltr-backup-storage-costs.xlsx
+++ b/src/python/ltr-cost-workbook/ltr-backup-storage-costs.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost matrix" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier comparison" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compression sensitivity" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Private endpoint variant" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -188,6 +189,9 @@
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -553,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -665,53 +669,74 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>5. 'Private endpoint variant' adds the cost of reaching the storage account privately. It is additive and does not change the other sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Private endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>If you reach the storage account over a private endpoint, the endpoint bills by the hour for as long as it exists, whether or not anything is using it. Over a multi-year retention that standing charge can exceed the cost of the data itself. The fix is to create the endpoint for the drain, delete it, and re-create it if someone ever needs to read the archive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>VERIFIED: all prices, taken from the Azure retail prices API (see 'Prices' for the exact retrieval timestamp). Transfer and storage arithmetic.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="39" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="27" ht="39" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>ASSUMED: the compression ratio. This is the weakest input and it drives the largest term. Measured ratios in testing ranged from 1.02x on incompressible data to 33x on highly repetitive data, against a default assumption of 4x. Budget with the worst ratio you actually observe.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>EXCLUDED: the compute cost of restoring each backup before exporting it. It is small and one-time. See Get-LtrExportCostEstimate.ps1 in the toolkit for that half.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Prices retrieved</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10T06:38:00.882590+00:00  |  region: eastus  |  USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10T06:51:02.761357+00:00  |  region: eastus  |  USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Caveat</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Retail prices exclude any enterprise agreement discount, reservation or credit.</t>
         </is>
@@ -1161,7 +1186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1185,7 +1210,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-10T06:38:00.882590+00:00 for region 'eastus' in USD. Product: General Block Blob v2. Data Stored is the first volume band (0-50 TB). Only the Hot tier is volume-banded; Cool, Cold and Archive are flat. Operation meters are not published for every redundancy; missing ones are substituted from the closest published redundancy and flagged in the Substituted column.</t>
+          <t>Retrieved 2026-09-10T06:51:02.761357+00:00 for region 'eastus' in USD. Product: General Block Blob v2. Data Stored is the first volume band (0-50 TB). Only the Hot tier is volume-banded; Cool, Cold and Archive are flat. Operation meters are not published for every redundancy; missing ones are substituted from the closest published redundancy and flagged in the Substituted column.</t>
         </is>
       </c>
     </row>
@@ -2039,6 +2064,89 @@
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Volume banding: the rest of this workbook prices everything at the first band. Only the Hot tier is banded, and the discount above 50 TB is roughly 4 percent, so for Hot scenarios above 50 TB the workbook is slightly conservative. Cool, Cold and Archive are flat at any volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Private endpoint and private DNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Private endpoint ($/hour)</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>Data processed, ingress ($/GB)</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Data processed, egress ($/GB)</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Private DNS zone ($/month, first 25)</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Private DNS queries ($/million)</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Private endpoint meters are published against region 'Global', not against an Azure region, so they are identical everywhere in the commercial cloud. Data processed is volume-banded (over 1,000,000 GB: $0.006; over 5,000,000 GB: $0.004); this workbook prices the first band, which holds for anything under 1 PB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Azure DNS prices private zones by geography zone rather than by region. These are the 'Zone 1' rates, which cover the commercial regions this model targets.</t>
         </is>
       </c>
     </row>
@@ -4075,4 +4183,777 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variant: reaching the storage account over a private endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>A private endpoint is not a one-off charge. It bills by the hour for as long as it exists, which changes the shape of the answer completely: for a compliance archive the endpoint can easily cost more than the data it protects. This sheet is additive; it does not alter the baseline model on the other sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Number of private endpoints</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>One per storage sub-resource. Blob only = 1; blob + dfs = 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Endpoint lifetime (months)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>How long the endpoint EXISTS, which is not necessarily the retention period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Hours per month</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>730</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Azure's standard billing month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated private DNS zone?</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>No if you already own privatelink.blob.core.windows.net; then its marginal cost is 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DNS queries per month (millions)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>An idle archive generates very few.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Drain traffic traverses the endpoint?</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>See the note at the bottom. Usually No, because the export is service-side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Read-back traverses the endpoint?</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>If you retrieve the artifacts from inside your VNet, it does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RATES (from the Prices sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Private endpoint $/hour</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <f>Prices!$B$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Data processed, ingress $/GB</t>
+        </is>
+      </c>
+      <c r="B16" s="10">
+        <f>Prices!$B$38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Data processed, egress $/GB</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>Prices!$B$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Private DNS zone $/month</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>Prices!$B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Private DNS queries $/million</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>Prices!$B$41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>COSTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Endpoint hours</t>
+        </is>
+      </c>
+      <c r="B22" s="12">
+        <f>$B$6*$B$7*$B$8*$B$15</f>
+        <v/>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>The standing charge. Usually the largest term on this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Private DNS zone</t>
+        </is>
+      </c>
+      <c r="B23" s="12">
+        <f>IF($B$9="Yes",$B$7*$B$18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Private DNS queries</t>
+        </is>
+      </c>
+      <c r="B24" s="12">
+        <f>$B$7*$B$10*$B$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Data processed on the drain (ingress)</t>
+        </is>
+      </c>
+      <c r="B25" s="12">
+        <f>IF($B$11="Yes",Parameters!$B$20*$B$16,0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Zero when the export is service-side, which is the normal case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Data processed on one full read-back (egress)</t>
+        </is>
+      </c>
+      <c r="B26" s="12">
+        <f>IF($B$12="Yes",Parameters!$B$20*$B$17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL private endpoint add-on</t>
+        </is>
+      </c>
+      <c r="B27" s="14">
+        <f>SUM($B$22:$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>COMPARED WITH THE BASELINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Storage-side total (from Parameters)</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>Parameters!$B$30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Private endpoint add-on</t>
+        </is>
+      </c>
+      <c r="B31" s="12">
+        <f>$B$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>COMBINED</t>
+        </is>
+      </c>
+      <c r="B32" s="43">
+        <f>$B$30+$B$31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Add-on as a multiple of the storage-side cost</t>
+        </is>
+      </c>
+      <c r="B33" s="44">
+        <f>IFERROR($B$31/$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Above 1 means the plumbing costs more than the data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Endpoint months</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Endpoint + DNS</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>Data processed</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>Add-on total</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>No private endpoint at all</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="29">
+        <f>$B$6*0*$B$8*$B$15+IF($B$9="Yes",0*$B$18,0)+0*$B$10*$B$19</f>
+        <v/>
+      </c>
+      <c r="D37" s="29">
+        <f>IF(0=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E37" s="32">
+        <f>$C37+$D37</f>
+        <v/>
+      </c>
+      <c r="F37" s="29">
+        <f>Parameters!$B$30+$E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>Endpoint only during the drain (1 month)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="12">
+        <f>$B$6*1*$B$8*$B$15+IF($B$9="Yes",1*$B$18,0)+1*$B$10*$B$19</f>
+        <v/>
+      </c>
+      <c r="D38" s="12">
+        <f>IF(1=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E38" s="34">
+        <f>$C38+$D38</f>
+        <v/>
+      </c>
+      <c r="F38" s="12">
+        <f>Parameters!$B$30+$E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>Endpoint kept for 3 months</t>
+        </is>
+      </c>
+      <c r="B39" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="29">
+        <f>$B$6*3*$B$8*$B$15+IF($B$9="Yes",3*$B$18,0)+3*$B$10*$B$19</f>
+        <v/>
+      </c>
+      <c r="D39" s="29">
+        <f>IF(3=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E39" s="32">
+        <f>$C39+$D39</f>
+        <v/>
+      </c>
+      <c r="F39" s="29">
+        <f>Parameters!$B$30+$E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>Endpoint kept for the full retention</t>
+        </is>
+      </c>
+      <c r="B40" s="36">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="C40" s="29">
+        <f>$B$6*$B$7*$B$8*$B$15+IF($B$9="Yes",$B$7*$B$18,0)+$B$7*$B$10*$B$19</f>
+        <v/>
+      </c>
+      <c r="D40" s="29">
+        <f>IF($B$7=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E40" s="32">
+        <f>$C40+$D40</f>
+        <v/>
+      </c>
+      <c r="F40" s="29">
+        <f>Parameters!$B$30+$E40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ADD-ON BY ENDPOINT LIFETIME AND COUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>Lifetime (months) \ endpoints</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" s="29">
+        <f>1*0*$B$8*$B$15+IF($B$9="Yes",0*$B$18,0)+0*$B$10*$B$19+IF(0=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="C44" s="29">
+        <f>2*0*$B$8*$B$15+IF($B$9="Yes",0*$B$18,0)+0*$B$10*$B$19+IF(0=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="D44" s="29">
+        <f>4*0*$B$8*$B$15+IF($B$9="Yes",0*$B$18,0)+0*$B$10*$B$19+IF(0=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E44" s="29">
+        <f>8*0*$B$8*$B$15+IF($B$9="Yes",0*$B$18,0)+0*$B$10*$B$19+IF(0=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="29">
+        <f>1*1*$B$8*$B$15+IF($B$9="Yes",1*$B$18,0)+1*$B$10*$B$19+IF(1=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="C45" s="29">
+        <f>2*1*$B$8*$B$15+IF($B$9="Yes",1*$B$18,0)+1*$B$10*$B$19+IF(1=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="D45" s="29">
+        <f>4*1*$B$8*$B$15+IF($B$9="Yes",1*$B$18,0)+1*$B$10*$B$19+IF(1=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E45" s="29">
+        <f>8*1*$B$8*$B$15+IF($B$9="Yes",1*$B$18,0)+1*$B$10*$B$19+IF(1=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="29">
+        <f>1*3*$B$8*$B$15+IF($B$9="Yes",3*$B$18,0)+3*$B$10*$B$19+IF(3=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="C46" s="29">
+        <f>2*3*$B$8*$B$15+IF($B$9="Yes",3*$B$18,0)+3*$B$10*$B$19+IF(3=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="D46" s="29">
+        <f>4*3*$B$8*$B$15+IF($B$9="Yes",3*$B$18,0)+3*$B$10*$B$19+IF(3=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E46" s="29">
+        <f>8*3*$B$8*$B$15+IF($B$9="Yes",3*$B$18,0)+3*$B$10*$B$19+IF(3=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B47" s="29">
+        <f>1*6*$B$8*$B$15+IF($B$9="Yes",6*$B$18,0)+6*$B$10*$B$19+IF(6=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="C47" s="29">
+        <f>2*6*$B$8*$B$15+IF($B$9="Yes",6*$B$18,0)+6*$B$10*$B$19+IF(6=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="D47" s="29">
+        <f>4*6*$B$8*$B$15+IF($B$9="Yes",6*$B$18,0)+6*$B$10*$B$19+IF(6=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E47" s="29">
+        <f>8*6*$B$8*$B$15+IF($B$9="Yes",6*$B$18,0)+6*$B$10*$B$19+IF(6=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B48" s="29">
+        <f>1*12*$B$8*$B$15+IF($B$9="Yes",12*$B$18,0)+12*$B$10*$B$19+IF(12=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="C48" s="29">
+        <f>2*12*$B$8*$B$15+IF($B$9="Yes",12*$B$18,0)+12*$B$10*$B$19+IF(12=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="D48" s="29">
+        <f>4*12*$B$8*$B$15+IF($B$9="Yes",12*$B$18,0)+12*$B$10*$B$19+IF(12=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E48" s="29">
+        <f>8*12*$B$8*$B$15+IF($B$9="Yes",12*$B$18,0)+12*$B$10*$B$19+IF(12=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B49" s="29">
+        <f>1*24*$B$8*$B$15+IF($B$9="Yes",24*$B$18,0)+24*$B$10*$B$19+IF(24=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="C49" s="29">
+        <f>2*24*$B$8*$B$15+IF($B$9="Yes",24*$B$18,0)+24*$B$10*$B$19+IF(24=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="D49" s="29">
+        <f>4*24*$B$8*$B$15+IF($B$9="Yes",24*$B$18,0)+24*$B$10*$B$19+IF(24=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E49" s="29">
+        <f>8*24*$B$8*$B$15+IF($B$9="Yes",24*$B$18,0)+24*$B$10*$B$19+IF(24=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="45" t="n">
+        <v>60</v>
+      </c>
+      <c r="B50" s="29">
+        <f>1*60*$B$8*$B$15+IF($B$9="Yes",60*$B$18,0)+60*$B$10*$B$19+IF(60=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="C50" s="29">
+        <f>2*60*$B$8*$B$15+IF($B$9="Yes",60*$B$18,0)+60*$B$10*$B$19+IF(60=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="D50" s="29">
+        <f>4*60*$B$8*$B$15+IF($B$9="Yes",60*$B$18,0)+60*$B$10*$B$19+IF(60=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E50" s="29">
+        <f>8*60*$B$8*$B$15+IF($B$9="Yes",60*$B$18,0)+60*$B$10*$B$19+IF(60=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="45" t="n">
+        <v>84</v>
+      </c>
+      <c r="B51" s="29">
+        <f>1*84*$B$8*$B$15+IF($B$9="Yes",84*$B$18,0)+84*$B$10*$B$19+IF(84=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="C51" s="29">
+        <f>2*84*$B$8*$B$15+IF($B$9="Yes",84*$B$18,0)+84*$B$10*$B$19+IF(84=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="D51" s="29">
+        <f>4*84*$B$8*$B$15+IF($B$9="Yes",84*$B$18,0)+84*$B$10*$B$19+IF(84=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+      <c r="E51" s="29">
+        <f>8*84*$B$8*$B$15+IF($B$9="Yes",84*$B$18,0)+84*$B$10*$B$19+IF(84=0,0,$B$25+$B$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Why the drain usually does NOT cross the endpoint:</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>'az sql db export' and the Managed Instance 'BACKUP TO URL' statement are executed by the SQL service itself, not by a machine in your VNet, so the write does not traverse your private endpoint and is not charged as data processed. The toggle above exists because it does traverse the endpoint if you stage the artifacts through your own VM or self-hosted sqlpackage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>The trap this creates:</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>If you lock the storage account to private endpoints only, that same service-side write is BLOCKED. You need the 'Allow trusted Microsoft services' network exception, or a resource-instance rule scoped to the SQL server or instance. Otherwise the drain fails and the private endpoint is not the reason you would expect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>The actionable conclusion:</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Do not leave the endpoint running for the retention period. Create it for the drain, delete it, and re-create it in minutes on the day someone actually needs to read the archive. A deleted endpoint costs nothing, and the blobs are unaffected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Not modelled here:</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>The VNet itself, any VM you stage through, and any VPN or ExpressRoute gateway you need to reach the endpoint from on-premises. A gateway starts around $0.19/hour, which dwarfs everything on this sheet. If you need one purely for this, model it separately and it will change your conclusion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B57:F58"/>
+    <mergeCell ref="A2:F3"/>
+    <mergeCell ref="B55:F56"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B59:F60"/>
+    <mergeCell ref="B53:F54"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>